--- a/새벽배송_손익분기_시뮬레이터.xlsx
+++ b/새벽배송_손익분기_시뮬레이터.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="가정값" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="손익" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="손익분기" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시나리오" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +24,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="#,##0&quot;원&quot;"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -69,6 +70,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="7">
@@ -130,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -181,6 +188,16 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -894,11 +911,11 @@
     <row r="22">
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>차량·냉장설비</t>
+          <t>냉장설비</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>1500000</v>
+        <v>500000</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
@@ -907,7 +924,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>리스·유지·냉장 인프라</t>
+          <t>냉장고·쇼케이스 유지·전기. 배송 차량은 용차(변동비)라 고정비에 넣지 않는다</t>
         </is>
       </c>
     </row>
@@ -1319,12 +1336,17 @@
     <row r="28">
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>차량·냉장설비</t>
+          <t>냉장설비</t>
         </is>
       </c>
       <c r="C28" s="10">
         <f>가정값!$C$22</f>
         <v/>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>배송 차량은 용차라 위 배송 섹션의 변동비로 잡힌다</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -2207,4 +2229,423 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B1:F25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>고정비 시나리오 비교 — 어느 규모로 시작할 것인가</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>노란 셀을 바꾸면 BEP가 자동 재계산됩니다 · 배송 차량은 용차(변동비)라 고정비에 넣지 않습니다</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>고정비 항목 (월)</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>A. 안정기</t>
+        </is>
+      </c>
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <t>B. 축소 운영</t>
+        </is>
+      </c>
+      <c r="E4" s="22" t="inlineStr">
+        <is>
+          <t>C. 최소 시작</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>주방 임대·관리비</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="D5" s="23" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E5" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>모회사 주방 공유 시 0 또는 분담</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>인건비</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="D6" s="23" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="E6" s="23" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>C는 겸업·파트타임 기준</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>냉장설비</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="n">
+        <v>500000</v>
+      </c>
+      <c r="D7" s="23" t="n">
+        <v>300000</v>
+      </c>
+      <c r="E7" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>배송 차량은 용차라 제외</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>마케팅비</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="D8" s="23" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="E8" s="23" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>초기엔 단지 단위 영업이 더 싸다</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>기타 운영비</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D9" s="23" t="n">
+        <v>700000</v>
+      </c>
+      <c r="E9" s="23" t="n">
+        <v>500000</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>SW·결제·보험·잡비</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>월 고정비 합계</t>
+        </is>
+      </c>
+      <c r="C10" s="12">
+        <f>SUM(C5:C9)</f>
+        <v/>
+      </c>
+      <c r="D10" s="12">
+        <f>SUM(D5:D9)</f>
+        <v/>
+      </c>
+      <c r="E10" s="12">
+        <f>SUM(E5:E9)</f>
+        <v/>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>항목 합계</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>손익분기 배송일당 집수</t>
+        </is>
+      </c>
+      <c r="C11" s="15">
+        <f>ROUNDUP(IF((C10/(((손익!$C$22+손익!$C$17)-가정값!$C$17)*손익!$C$4))&gt;=손익!$C$7,(C10/(((손익!$C$22+손익!$C$17)-가정값!$C$17)*손익!$C$4)),((C10/손익!$C$4+가정값!$C$16)/(손익!$C$22+손익!$C$17))),0)</f>
+        <v/>
+      </c>
+      <c r="D11" s="15">
+        <f>ROUNDUP(IF((D10/(((손익!$C$22+손익!$C$17)-가정값!$C$17)*손익!$C$4))&gt;=손익!$C$7,(D10/(((손익!$C$22+손익!$C$17)-가정값!$C$17)*손익!$C$4)),((D10/손익!$C$4+가정값!$C$16)/(손익!$C$22+손익!$C$17))),0)</f>
+        <v/>
+      </c>
+      <c r="E11" s="15">
+        <f>ROUNDUP(IF((E10/(((손익!$C$22+손익!$C$17)-가정값!$C$17)*손익!$C$4))&gt;=손익!$C$7,(E10/(((손익!$C$22+손익!$C$17)-가정값!$C$17)*손익!$C$4)),((E10/손익!$C$4+가정값!$C$16)/(손익!$C$22+손익!$C$17))),0)</f>
+        <v/>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>이 집수를 넘으면 흑자. 분기점 미만 구간은 보장액을 반영해 계산</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>손익분기 월 주문 건수</t>
+        </is>
+      </c>
+      <c r="C12" s="15">
+        <f>C11*손익!$C$4</f>
+        <v/>
+      </c>
+      <c r="D12" s="15">
+        <f>D11*손익!$C$4</f>
+        <v/>
+      </c>
+      <c r="E12" s="15">
+        <f>E11*손익!$C$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>현재 가정 물량의 월 영업이익</t>
+        </is>
+      </c>
+      <c r="C13" s="12">
+        <f>손익!$C$22*손익!$C$5-C10</f>
+        <v/>
+      </c>
+      <c r="D13" s="12">
+        <f>손익!$C$22*손익!$C$5-D10</f>
+        <v/>
+      </c>
+      <c r="E13" s="12">
+        <f>손익!$C$22*손익!$C$5-E10</f>
+        <v/>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>가정값 시트의 '배송일당 주문 수' 기준</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>물량별 월 영업이익 비교</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n"/>
+      <c r="D15" s="3" t="n"/>
+      <c r="E15" s="3" t="n"/>
+      <c r="F15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>배송일당 집수</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>A. 안정기</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>B. 축소 운영</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>C. 최소 시작</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="C17" s="10">
+        <f>((손익!$C$22+손익!$C$17)-(MAX(MAX(1,CEILING($B$17/가정값!$C$18,1))*가정값!$C$16,$B$17*가정값!$C$17)/$B$17))*$B$17*손익!$C$4-C10</f>
+        <v/>
+      </c>
+      <c r="D17" s="10">
+        <f>((손익!$C$22+손익!$C$17)-(MAX(MAX(1,CEILING($B$17/가정값!$C$18,1))*가정값!$C$16,$B$17*가정값!$C$17)/$B$17))*$B$17*손익!$C$4-D10</f>
+        <v/>
+      </c>
+      <c r="E17" s="10">
+        <f>((손익!$C$22+손익!$C$17)-(MAX(MAX(1,CEILING($B$17/가정값!$C$18,1))*가정값!$C$16,$B$17*가정값!$C$17)/$B$17))*$B$17*손익!$C$4-E10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="9" t="n">
+        <v>80</v>
+      </c>
+      <c r="C18" s="10">
+        <f>((손익!$C$22+손익!$C$17)-(MAX(MAX(1,CEILING($B$18/가정값!$C$18,1))*가정값!$C$16,$B$18*가정값!$C$17)/$B$18))*$B$18*손익!$C$4-C10</f>
+        <v/>
+      </c>
+      <c r="D18" s="10">
+        <f>((손익!$C$22+손익!$C$17)-(MAX(MAX(1,CEILING($B$18/가정값!$C$18,1))*가정값!$C$16,$B$18*가정값!$C$17)/$B$18))*$B$18*손익!$C$4-D10</f>
+        <v/>
+      </c>
+      <c r="E18" s="10">
+        <f>((손익!$C$22+손익!$C$17)-(MAX(MAX(1,CEILING($B$18/가정값!$C$18,1))*가정값!$C$16,$B$18*가정값!$C$17)/$B$18))*$B$18*손익!$C$4-E10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="C19" s="10">
+        <f>((손익!$C$22+손익!$C$17)-(MAX(MAX(1,CEILING($B$19/가정값!$C$18,1))*가정값!$C$16,$B$19*가정값!$C$17)/$B$19))*$B$19*손익!$C$4-C10</f>
+        <v/>
+      </c>
+      <c r="D19" s="10">
+        <f>((손익!$C$22+손익!$C$17)-(MAX(MAX(1,CEILING($B$19/가정값!$C$18,1))*가정값!$C$16,$B$19*가정값!$C$17)/$B$19))*$B$19*손익!$C$4-D10</f>
+        <v/>
+      </c>
+      <c r="E19" s="10">
+        <f>((손익!$C$22+손익!$C$17)-(MAX(MAX(1,CEILING($B$19/가정값!$C$18,1))*가정값!$C$16,$B$19*가정값!$C$17)/$B$19))*$B$19*손익!$C$4-E10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="9" t="n">
+        <v>150</v>
+      </c>
+      <c r="C20" s="10">
+        <f>((손익!$C$22+손익!$C$17)-(MAX(MAX(1,CEILING($B$20/가정값!$C$18,1))*가정값!$C$16,$B$20*가정값!$C$17)/$B$20))*$B$20*손익!$C$4-C10</f>
+        <v/>
+      </c>
+      <c r="D20" s="10">
+        <f>((손익!$C$22+손익!$C$17)-(MAX(MAX(1,CEILING($B$20/가정값!$C$18,1))*가정값!$C$16,$B$20*가정값!$C$17)/$B$20))*$B$20*손익!$C$4-D10</f>
+        <v/>
+      </c>
+      <c r="E20" s="10">
+        <f>((손익!$C$22+손익!$C$17)-(MAX(MAX(1,CEILING($B$20/가정값!$C$18,1))*가정값!$C$16,$B$20*가정값!$C$17)/$B$20))*$B$20*손익!$C$4-E10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="9" t="n">
+        <v>200</v>
+      </c>
+      <c r="C21" s="10">
+        <f>((손익!$C$22+손익!$C$17)-(MAX(MAX(1,CEILING($B$21/가정값!$C$18,1))*가정값!$C$16,$B$21*가정값!$C$17)/$B$21))*$B$21*손익!$C$4-C10</f>
+        <v/>
+      </c>
+      <c r="D21" s="10">
+        <f>((손익!$C$22+손익!$C$17)-(MAX(MAX(1,CEILING($B$21/가정값!$C$18,1))*가정값!$C$16,$B$21*가정값!$C$17)/$B$21))*$B$21*손익!$C$4-D10</f>
+        <v/>
+      </c>
+      <c r="E21" s="10">
+        <f>((손익!$C$22+손익!$C$17)-(MAX(MAX(1,CEILING($B$21/가정값!$C$18,1))*가정값!$C$16,$B$21*가정값!$C$17)/$B$21))*$B$21*손익!$C$4-E10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="9" t="n">
+        <v>300</v>
+      </c>
+      <c r="C22" s="10">
+        <f>((손익!$C$22+손익!$C$17)-(MAX(MAX(1,CEILING($B$22/가정값!$C$18,1))*가정값!$C$16,$B$22*가정값!$C$17)/$B$22))*$B$22*손익!$C$4-C10</f>
+        <v/>
+      </c>
+      <c r="D22" s="10">
+        <f>((손익!$C$22+손익!$C$17)-(MAX(MAX(1,CEILING($B$22/가정값!$C$18,1))*가정값!$C$16,$B$22*가정값!$C$17)/$B$22))*$B$22*손익!$C$4-D10</f>
+        <v/>
+      </c>
+      <c r="E22" s="10">
+        <f>((손익!$C$22+손익!$C$17)-(MAX(MAX(1,CEILING($B$22/가정값!$C$18,1))*가정값!$C$16,$B$22*가정값!$C$17)/$B$22))*$B$22*손익!$C$4-E10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="9" t="n">
+        <v>400</v>
+      </c>
+      <c r="C23" s="10">
+        <f>((손익!$C$22+손익!$C$17)-(MAX(MAX(1,CEILING($B$23/가정값!$C$18,1))*가정값!$C$16,$B$23*가정값!$C$17)/$B$23))*$B$23*손익!$C$4-C10</f>
+        <v/>
+      </c>
+      <c r="D23" s="10">
+        <f>((손익!$C$22+손익!$C$17)-(MAX(MAX(1,CEILING($B$23/가정값!$C$18,1))*가정값!$C$16,$B$23*가정값!$C$17)/$B$23))*$B$23*손익!$C$4-D10</f>
+        <v/>
+      </c>
+      <c r="E23" s="10">
+        <f>((손익!$C$22+손익!$C$17)-(MAX(MAX(1,CEILING($B$23/가정값!$C$18,1))*가정값!$C$16,$B$23*가정값!$C$17)/$B$23))*$B$23*손익!$C$4-E10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>※ 고정비를 100만 원 줄이면 BEP가 약 14~15집 내려갑니다. 수요가 불확실한 초기에는 고정비를 변동비로 바꾸는 편이 안전합니다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/새벽배송_손익분기_시뮬레이터.xlsx
+++ b/새벽배송_손익분기_시뮬레이터.xlsx
@@ -564,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E24"/>
+  <dimension ref="B1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -791,7 +791,7 @@
     <row r="15" ht="22" customHeight="1">
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>③ 배송 가정 (최소비용 보장 용역)</t>
+          <t>③ 배송 가정 (최소비용 보장 용역 · 전량 용차 기준)</t>
         </is>
       </c>
       <c r="C15" s="3" t="n"/>
@@ -911,31 +911,31 @@
     <row r="22">
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>냉장설비</t>
+          <t>냉장고 1대당 감당 집수</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>500000</v>
+        <v>100</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>원</t>
+          <t>집</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>냉장고·쇼케이스 유지·전기. 배송 차량은 용차(변동비)라 고정비에 넣지 않는다</t>
+          <t>완제품 보관 기준. 집당 평균 2~3개 × 1회 배송분</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>마케팅비</t>
+          <t>냉장고 1대 월 비용</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>3000000</v>
+        <v>150000</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
@@ -944,25 +944,45 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>신규 유입 광고 (초기 공격 시 ↑)</t>
+          <t>감가상각 + 전기 + 유지보수. 워크인 냉장실이면 대당 캐파·비용 모두 ↑</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="4" t="inlineStr">
         <is>
+          <t>마케팅비</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>원</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>신규 유입 광고 (초기 공격 시 ↑)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="4" t="inlineStr">
+        <is>
           <t>기타 운영비</t>
         </is>
       </c>
-      <c r="C24" s="5" t="n">
+      <c r="C25" s="5" t="n">
         <v>1000000</v>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>원</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>SW·결제·보험·잡비</t>
         </is>
@@ -1336,16 +1356,16 @@
     <row r="28">
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>냉장설비</t>
+          <t>냉장설비 (완제품 보관)</t>
         </is>
       </c>
       <c r="C28" s="10">
-        <f>가정값!$C$22</f>
+        <f>MAX(1,CEILING(가정값!$C$6/가정값!$C$22,1))*가정값!$C$23</f>
         <v/>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>배송 차량은 용차라 위 배송 섹션의 변동비로 잡힌다</t>
+          <t>필요 대수 = 배송일당 집수 ÷ 대당 캐파 (올림). 물량이 늘면 계단식 증가</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1376,7 @@
         </is>
       </c>
       <c r="C29" s="10">
-        <f>가정값!$C$23</f>
+        <f>가정값!$C$24</f>
         <v/>
       </c>
     </row>
@@ -1367,7 +1387,7 @@
         </is>
       </c>
       <c r="C30" s="10">
-        <f>가정값!$C$24</f>
+        <f>가정값!$C$25</f>
         <v/>
       </c>
     </row>
@@ -1528,7 +1548,7 @@
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>※ 위 BEP는 현재 가정값의 건당 배송비를 그대로 적용한 값입니다. 물량이 코스 분기점 미만이면 배송비가 올라가므로 아래 민감도 표를 함께 보세요.</t>
+          <t>※ 위 BEP는 현재 가정값(배송일당 주문 수) 기준의 배송비·냉장설비를 적용한 값입니다. 두 항목 모두 물량에 따라 달라지므로, 정확히 보려면 가정값의 주문 수를 BEP 근처로 맞춘 뒤 다시 확인하세요.</t>
         </is>
       </c>
     </row>
@@ -2329,11 +2349,11 @@
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>냉장설비</t>
+          <t>냉장설비 (완제품 보관)</t>
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>500000</v>
+        <v>450000</v>
       </c>
       <c r="D7" s="23" t="n">
         <v>300000</v>
@@ -2343,7 +2363,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>배송 차량은 용차라 제외</t>
+          <t>물량에 따라 계단식 증설 · C는 모회사 시설 공유 가정</t>
         </is>
       </c>
     </row>

--- a/새벽배송_손익분기_시뮬레이터.xlsx
+++ b/새벽배송_손익분기_시뮬레이터.xlsx
@@ -564,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E25"/>
+  <dimension ref="B1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -911,31 +911,31 @@
     <row r="22">
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>냉장고 1대당 감당 집수</t>
+          <t>냉장 보관 (완제품)</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>집</t>
+          <t>원</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>완제품 보관 기준. 집당 평균 2~3개 × 1회 배송분</t>
+          <t>10평 워크인 냉장실 보유 — 추가 증설 불필요. 분담금·증설분이 생기면 입력</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>냉장고 1대 월 비용</t>
+          <t>마케팅비</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>150000</v>
+        <v>3000000</v>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
@@ -944,18 +944,18 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>감가상각 + 전기 + 유지보수. 워크인 냉장실이면 대당 캐파·비용 모두 ↑</t>
+          <t>신규 유입 광고 (초기 공격 시 ↑)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>마케팅비</t>
+          <t>기타 운영비</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>3000000</v>
+        <v>1000000</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
@@ -963,26 +963,6 @@
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>신규 유입 광고 (초기 공격 시 ↑)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>기타 운영비</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>원</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>SW·결제·보험·잡비</t>
         </is>
@@ -1356,16 +1336,16 @@
     <row r="28">
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>냉장설비 (완제품 보관)</t>
+          <t>냉장 보관 (완제품)</t>
         </is>
       </c>
       <c r="C28" s="10">
-        <f>MAX(1,CEILING(가정값!$C$6/가정값!$C$22,1))*가정값!$C$23</f>
+        <f>가정값!$C$22</f>
         <v/>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>필요 대수 = 배송일당 집수 ÷ 대당 캐파 (올림). 물량이 늘면 계단식 증가</t>
+          <t>모회사 10평 워크인 공유 — 현재 추가 비용 없음</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1356,7 @@
         </is>
       </c>
       <c r="C29" s="10">
-        <f>가정값!$C$24</f>
+        <f>가정값!$C$23</f>
         <v/>
       </c>
     </row>
@@ -1387,7 +1367,7 @@
         </is>
       </c>
       <c r="C30" s="10">
-        <f>가정값!$C$25</f>
+        <f>가정값!$C$24</f>
         <v/>
       </c>
     </row>
@@ -1548,7 +1528,7 @@
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>※ 위 BEP는 현재 가정값(배송일당 주문 수) 기준의 배송비·냉장설비를 적용한 값입니다. 두 항목 모두 물량에 따라 달라지므로, 정확히 보려면 가정값의 주문 수를 BEP 근처로 맞춘 뒤 다시 확인하세요.</t>
+          <t>※ 위 BEP는 현재 가정값(배송일당 주문 수) 기준의 배송비를 적용한 값입니다. 배송비는 물량에 따라 달라지므로, 정확히 보려면 가정값의 주문 수를 BEP 근처로 맞춘 뒤 다시 확인하세요.</t>
         </is>
       </c>
     </row>
@@ -2349,21 +2329,21 @@
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>냉장설비 (완제품 보관)</t>
+          <t>냉장 보관 (완제품)</t>
         </is>
       </c>
       <c r="C7" s="23" t="n">
-        <v>450000</v>
+        <v>0</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="E7" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>물량에 따라 계단식 증설 · C는 모회사 시설 공유 가정</t>
+          <t>10평 워크인 보유 — 증설 시에만 입력</t>
         </is>
       </c>
     </row>
